--- a/outputs/daily/hr_rankings_2026-09-19_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-19_full.xlsx
@@ -1378,34 +1378,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11534,34 +11530,30 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12094,34 +12086,30 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -13722,34 +13710,30 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -19534,34 +19518,30 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -26612,28 +26592,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr"/>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y96" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -36926,34 +36910,30 @@
       </c>
       <c r="W134" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB134" t="inlineStr"/>
       <c r="AC134" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -41626,34 +41606,30 @@
       </c>
       <c r="W151" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB151" t="inlineStr"/>
       <c r="AC151" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -52120,28 +52096,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W189" t="inlineStr"/>
-      <c r="X189" t="inlineStr"/>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y189" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB189" t="inlineStr"/>
       <c r="AC189" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -73184,34 +73164,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
